--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/WASHINGTON_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/WASHINGTON_2016.xlsx
@@ -2389,7 +2389,7 @@
         <v>99</v>
       </c>
       <c r="D113">
-        <v>0.009235936188077247</v>
+        <v>0.009235936188077248</v>
       </c>
     </row>
     <row r="114">
@@ -2839,7 +2839,7 @@
         <v>10</v>
       </c>
       <c r="D138">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="139">
@@ -3271,7 +3271,7 @@
         <v>10</v>
       </c>
       <c r="D162">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="163">
@@ -3541,7 +3541,7 @@
         <v>10</v>
       </c>
       <c r="D177">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="178">
@@ -4027,7 +4027,7 @@
         <v>10</v>
       </c>
       <c r="D204">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="205">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C241">
@@ -5377,7 +5377,7 @@
         <v>10</v>
       </c>
       <c r="D279">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="280">
@@ -5647,7 +5647,7 @@
         <v>10</v>
       </c>
       <c r="D294">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="295">
@@ -6925,7 +6925,7 @@
         <v>10</v>
       </c>
       <c r="D365">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="366">
@@ -7447,7 +7447,7 @@
         <v>10</v>
       </c>
       <c r="D394">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="395">
@@ -8095,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="D430">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="431">
@@ -8545,7 +8545,7 @@
         <v>10</v>
       </c>
       <c r="D455">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="456">
@@ -8959,7 +8959,7 @@
         <v>10</v>
       </c>
       <c r="D478">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="479">
@@ -9031,7 +9031,7 @@
         <v>10</v>
       </c>
       <c r="D482">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="483">
@@ -9553,7 +9553,7 @@
         <v>10</v>
       </c>
       <c r="D511">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="512">
@@ -9607,7 +9607,7 @@
         <v>10</v>
       </c>
       <c r="D514">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="515">
@@ -11785,7 +11785,7 @@
         <v>10</v>
       </c>
       <c r="D635">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="636">
@@ -12307,7 +12307,7 @@
         <v>10</v>
       </c>
       <c r="D664">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="665">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C754">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 26-</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C755">
@@ -14449,7 +14449,7 @@
         <v>10</v>
       </c>
       <c r="D783">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="784">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C788">
@@ -15493,7 +15493,7 @@
         <v>107</v>
       </c>
       <c r="D841">
-        <v>0.009982274465901671</v>
+        <v>0.009982274465901672</v>
       </c>
     </row>
     <row r="842">
@@ -16879,7 +16879,7 @@
         <v>10</v>
       </c>
       <c r="D918">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="919">
@@ -19561,7 +19561,7 @@
         <v>10</v>
       </c>
       <c r="D1067">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="1068">
@@ -22081,7 +22081,7 @@
         <v>10</v>
       </c>
       <c r="D1207">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="1208">
@@ -22333,7 +22333,7 @@
         <v>10</v>
       </c>
       <c r="D1221">
-        <v>0.0009329228472805299</v>
+        <v>0.00093292284728053</v>
       </c>
     </row>
     <row r="1222">
